--- a/CAD/BOM/BOM.xlsx
+++ b/CAD/BOM/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\goudard\VO2max\CAD\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{250246C7-3559-40FA-B5E4-10149A0B645A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C07D163-DCAD-47A4-B469-1C7158DDB18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37620" yWindow="780" windowWidth="28800" windowHeight="15285" xr2:uid="{E19CAD4D-15A0-4A52-A355-CBFF32A63223}"/>
+    <workbookView xWindow="2340" yWindow="2610" windowWidth="28800" windowHeight="15285" xr2:uid="{E19CAD4D-15A0-4A52-A355-CBFF32A63223}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Board</t>
   </si>
@@ -82,12 +82,51 @@
   </si>
   <si>
     <t>on/off switch</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>AliExpress (https://fr.aliexpress.com/item/4000231063473.html?spm=a2g0o.order_detail.order_detail_item.3.503c7d56OnTloD&amp;gatewayAdapt=glo2fra)</t>
+  </si>
+  <si>
+    <t>RS (https://fr.rs-online.com/web/p/piles-rechargeables-taille-speciale/1449405)</t>
+  </si>
+  <si>
+    <t>Farnell (https://fr.farnell.com/dfrobot/sen0372/module-capteur-de-pression-carte/dp/3974103)</t>
+  </si>
+  <si>
+    <t>RS (https://fr.rs-online.com/web/p/ci-de-capteur-de-pression/1331913)</t>
+  </si>
+  <si>
+    <t>Farnell (https://fr.farnell.com/dfrobot/sen0322/module-capteur-i2c-oxygen-carte/dp/3879708)</t>
+  </si>
+  <si>
+    <t>RS (https://fr.rs-online.com/web/p/capteurs-de-temperature-et-d-humidite/1720552)</t>
+  </si>
+  <si>
+    <t>RS (https://fr.rs-online.com/web/p/masques-respiratoires/0766378?gb=a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="7" formatCode="&quot;€&quot;#,##0.00_);\(&quot;€&quot;#,##0.00\)"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -117,8 +156,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -433,75 +473,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A946CF87-8BEB-4E90-9D71-7C94CCCCC820}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="3" width="44.28515625" customWidth="1"/>
+    <col min="2" max="2" width="44.28515625" customWidth="1"/>
+    <col min="3" max="3" width="145.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>14</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D11" s="1">
+        <f>SUM(D2:D8)</f>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>